--- a/insurance_data/4_life/property/extracted_data.xlsx
+++ b/insurance_data/4_life/property/extracted_data.xlsx
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8,688 원</t>
+          <t>8,649 원</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8,688 원</t>
+          <t>8,649 원</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>8,688</t>
+          <t>8,649</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8,688</t>
+          <t>8,649</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1,731 원</t>
+          <t>1,637 원</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1,731 원</t>
+          <t>1,637 원</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2569,22 +2569,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1,731</t>
+          <t>1,637</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1,731</t>
+          <t>1,637</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2994,32 +2994,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>임차자배상책임(화재)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2,766 원</t>
+          <t>830 원</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2,766 원</t>
+          <t>830 원</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3041,42 +3041,42 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>임차자배상책임(화재)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2,766</t>
+          <t>830</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2,766</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>도난손해(주택)(실손전부형)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3154,17 +3154,17 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>도난손해(주택)(실손전부형)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3210,16 +3210,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -3236,17 +3240,13 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3290,22 +3290,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>주택화재임시거주비(4일이상)</t>
+          <t>화재손해</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
+          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -3326,17 +3326,17 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>주택화재임시거주비(4일이상)</t>
+          <t>화재손해</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
+          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -3372,36 +3372,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ</t>
+          <t>가족화재벌금</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
+          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2,766 원</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2,766 원</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -3414,27 +3422,51 @@
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>롯데손보</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>(무) let:care 재물종합보험(2604)</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ</t>
+          <t>가족화재벌금</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
+          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2,766</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2,766</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -3464,7 +3496,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3474,18 +3506,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>도난손해(주택)(실손전부형)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -3504,11 +3540,19 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>도난손해(주택)(실손전부형)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -3544,7 +3588,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3554,24 +3598,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>화재손해(실손)</t>
+          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
+          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -3590,19 +3626,15 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>화재손해(실손)</t>
+          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
+          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -3636,44 +3668,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>(무) let:care 화재배상책임보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>임차자배상책임(화재)</t>
+          <t>주택화재임시거주비(4일이상)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
+          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>1일당 보험가입금액</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>830 원</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>830 원</t>
-        </is>
-      </c>
+          <t>1일당 보험가입금액</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -3686,51 +3710,27 @@
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>롯데손보</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>(무) let:care 화재배상책임보험(2601)</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>임차자배상책임(화재)</t>
+          <t>주택화재임시거주비(4일이상)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
+          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
+          <t>1일당 보험가입금액</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>(무) let:care 화재배상책임보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임(다중이용업소제외)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>보험목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해 보상</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억 5천만원 한도, 부상 3천만원 한도, 대물(1사고당) : 보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억 5천만원 한도, 부상 3천만원 한도, 대물(1사고당) : 보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -3806,17 +3806,17 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임(다중이용업소제외)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>보험목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해 보상</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억 5천만원 한도, 부상 3천만원 한도, 대물(1사고당) : 보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>(무) let:care 화재배상책임보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3862,16 +3862,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임(무과실책임포함,다중이용업소)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>보험목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해 보상. 단, ·다중이용업소의 안전관리에 관한 특별법· 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -3888,17 +3892,13 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>화재(폭발포함)배상책임(무과실책임포함,다중이용업소)</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>보험목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해 보상. 단, ·다중이용업소의 안전관리에 관한 특별법· 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(무) let:care 화재배상책임보험(2601)</t>
+          <t>(무) let:care 재물종합보험(2604)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>화재손해</t>
+          <t>화재손해(실손)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3978,7 +3978,7 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>화재손해</t>
+          <t>화재손해(실손)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -11402,32 +11402,32 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>가스사고배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1,885 원</t>
+          <t>26,592 원</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1,885 원</t>
+          <t>26,592 원</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -11449,42 +11449,42 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>가스사고배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>1,885</t>
+          <t>26,592</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>1,885</t>
+          <t>26,592</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr"/>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -11526,22 +11526,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
+          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -11562,17 +11562,17 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
+          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -11618,22 +11618,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>주택(화재)건물재조달차액지원(실손)</t>
+          <t>배상책임종합보장(실손)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
+          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -11654,17 +11654,17 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr">
         <is>
-          <t>주택(화재)건물재조달차액지원(실손)</t>
+          <t>배상책임종합보장(실손)</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
+          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W119" t="inlineStr"/>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -11710,22 +11710,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
+          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
+          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -11746,17 +11746,17 @@
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr">
         <is>
-          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
+          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
+          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W120" t="inlineStr"/>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -11802,22 +11802,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>재산손해종합보장(실손보상)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -11838,17 +11838,17 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>재산손해종합보장(실손보상)</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W121" t="inlineStr"/>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -11894,22 +11894,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>화재손해(실손보상)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -11930,17 +11930,17 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr">
         <is>
-          <t>화재손해(실손보상)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="W122" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -11986,32 +11986,32 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>가스사고배상책임Ⅱ(실손)</t>
+          <t>뇌혈관질환진단비</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
+          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>26,592 원</t>
+          <t>97,490 원</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>26,592 원</t>
+          <t>82,750 원</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -12033,42 +12033,42 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>가스사고배상책임Ⅱ(실손)</t>
+          <t>뇌혈관질환진단비</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
+          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>26,592</t>
+          <t>97,490</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>26,592</t>
+          <t>82,750</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr"/>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12110,22 +12110,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -12146,17 +12146,17 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="W124" t="inlineStr"/>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -12202,22 +12202,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>배상책임종합보장(실손)</t>
+          <t>암진단비Ⅱ(유사암제외)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
+          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -12238,17 +12238,17 @@
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr">
         <is>
-          <t>배상책임종합보장(실손)</t>
+          <t>암진단비Ⅱ(유사암제외)</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
+          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="W125" t="inlineStr"/>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -12294,22 +12294,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
+          <t>항암방사선약물치료비(유사암포함)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
+          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -12330,17 +12330,17 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr">
         <is>
-          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
+          <t>항암방사선약물치료비(유사암포함)</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
+          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="W126" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -12386,24 +12386,16 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>재산손해종합보장(실손보상)</t>
+          <t>허혈심장질환진단비</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
+          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
@@ -12422,19 +12414,15 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
-          <t>재산손해종합보장(실손보상)</t>
+          <t>허혈심장질환진단비</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
+          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
@@ -12468,36 +12456,44 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1,885 원</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1,885 원</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
@@ -12510,27 +12506,51 @@
         </is>
       </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>(무)참좋은화재플러스보장보험2604</t>
+        </is>
+      </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
-      <c r="Y128" t="inlineStr"/>
-      <c r="Z128" t="inlineStr"/>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
@@ -12560,44 +12580,36 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>뇌혈관질환진단비</t>
+          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>97,490 원</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>82,750 원</t>
-        </is>
-      </c>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
@@ -12610,51 +12622,27 @@
         </is>
       </c>
       <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>DB손보</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
-        </is>
-      </c>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>뇌혈관질환진단비</t>
+          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>97,490</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>82,750</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>98.5</t>
-        </is>
-      </c>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr"/>
@@ -12684,7 +12672,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -12694,22 +12682,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>주택(화재)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
+          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>보험가입금액(1억원)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>보험가입금액(1억원)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -12730,17 +12718,17 @@
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>주택(화재)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
+          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>보험가입금액(1억원)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W130" t="inlineStr"/>
@@ -12776,7 +12764,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -12786,22 +12774,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>암진단비Ⅱ(유사암제외)</t>
+          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
+          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)</t>
+          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)</t>
+          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -12822,17 +12810,17 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr">
         <is>
-          <t>암진단비Ⅱ(유사암제외)</t>
+          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
+          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)</t>
+          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
         </is>
       </c>
       <c r="W131" t="inlineStr"/>
@@ -12868,7 +12856,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -12878,22 +12866,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>항암방사선약물치료비(유사암포함)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -12914,17 +12902,17 @@
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr">
         <is>
-          <t>항암방사선약물치료비(유사암포함)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>보험가입금액(2,000만원)</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="W132" t="inlineStr"/>
@@ -12960,7 +12948,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
+          <t>(무)참좋은화재플러스보장보험2604</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -12970,16 +12958,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>허혈심장질환진단비</t>
+          <t>화재손해(실손보상)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
@@ -12998,15 +12994,19 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr">
         <is>
-          <t>허혈심장질환진단비</t>
+          <t>화재손해(실손보상)</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr"/>
+          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
+        </is>
+      </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
